--- a/data_extactor/batch_10_fa/batch_0081_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0081_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | نرم‌افزار مسیریابی | نرم‌افزار دستور کار</t>
+          <t>Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب | نرم‌افزار دستور کار</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن‌گفتن | مانیتورینگ | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چالاکی دست | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | انعطاف‌پذیری گسترده | قدرت ایستا | چالاکی انگشتان | درک شفاهی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | بیان شفاهی | درک کتبی | تجسم فضایی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک عمق | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن</t>
+          <t>مهارت دستی | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | مهارت انگشتان | درک شفاهی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | بیان شفاهی | درک کتبی | تجسم | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک عمق | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | قرارگیری در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | قرارگیری در معرض ارتفاعات بالا | قرارگیری در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | اهمیت دقیق یا منظم بودن | سر و کار داشتن با مشتریان خارجی یا عموم مردم | فضای بسته، بدون کنترل محیطی | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرارگیری در معرض آلاینده‌ها | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فضای باز، زیر سقف | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرارگیری در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، زیر سقف | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصابان و تعمیرکاران شیشه خودرو | نجاران | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | برقی‌کاران | نصابان و تعمیرکاران تجهیزات الکترونیکی وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله برقی | نصابان حصار | شیشه‌بران | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | کارگران عایق‌کاری کف، سقف و دیوار | قفل‌سازان و تعمیرکاران گاوصندوق | کارگران عمومی نگهداری و تعمیرات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | تعمیرکاران واگن‌های ریلی | کارگران ورق‌کاری | کارگران آهن و فولاد سازه‌ای</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | نجّاران | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | برق‌کاران | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله برقی | نصابان حصار | شیشه‌بران | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری کف، سقف و دیوار | قفل‌سازان و تعمیرکاران گاوصندوق | کارگران نگهداری و تعمیرات عمومی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تعمیرکنندگان واگن‌های ریلی | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Emerson FIRSTVUE Value Sizing | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | IBM Maximo Asset Management | Ladder Logic | نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار SAP | Structured query language SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Wonderware software</t>
+          <t>Autodesk AutoCAD | Emerson FIRSTVUE Value Sizing | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | IBM Maximo Asset Management | Ladder Logic | نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار Wonderware</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن‌گفتن | گوش دادن فعال | نگارش | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | خدمات مشتریان و پرسنلی | کامپیوتر و الکترونیک | ریاضیات | طراحی | تولید و فرآوری</t>
+          <t>مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | طراحی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | چالاکی دست | تشخیص گفتار | انعطاف‌پذیری گسترده | هماهنگی چند عضو | چالاکی انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | دقت کنترل | وضوح گفتار</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | دقت کنترل | وضوح گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | گفتگوهای تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارگران | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | آزادی در تصمیم‌گیری | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فشار زمانی | فضای بسته، بدون کنترل محیطی | ایمیل | قرارگیری در معرض دماهای بسیار گرم یا سرد | قرارگیری در معرض شرایط خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرارگیری در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | قرارگیری در معرض تجهیزات خطرناک | قرارگیری در معرض شرایط نوری بسیار روشن یا نامناسب | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سر و کار داشتن با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | ایمیل | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض شرایط خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان | فناوریست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه‌ها، پست‌های برق و رله‌ها | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان مکانیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | تعمیرکاران واگن‌های ریلی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان مکانیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | تعمیرکنندگان واگن‌های ریلی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Alerton Ascent Compass | Atlas Construction Business Forms | Autodesk AutoCAD | نرم‌افزار اتوماسیون ساختمان | سیستم مدیریت تعمیر و نگهداری کامپیوتری CMMS | سیستم‌های مدیریت مخاطبین | Cworks CMMS | نرم‌افزار ثبت داده‌ها | نرم‌افزار پایگاه داده | Delta Controls inteliWEB | نرم‌افزار مدیریت انرژی ساختمان | نرم‌افزار گرافیکی | نرم‌افزار ابزارهای HVAC | Honeywell WEBs-N4 | IBM Maximo Asset Management | IBM Notes | Johnson Controls Metasys | ManagerPlus | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | Siemens APOGEE Building Automation Software</t>
+          <t>Adobe Acrobat | Alerton Ascent Compass | Atlas Construction Business Forms | Autodesk AutoCAD | نرم‌افزار اتوماسیون ساختمان | سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم‌های مدیریت مخاطبین | Cworks CMMS | نرم‌افزار ثبت داده‌ها | نرم‌افزار پایگاه داده | Delta Controls inteliWEB | نرم‌افزار مدیریت انرژی ساختمان | نرم‌افزار گرافیکی | نرم‌افزار ابزارهای HVAC | Honeywell WEBs-N4 | IBM Maximo Asset Management | IBM Notes | Johnson Controls Metasys | ManagerPlus | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | Siemens APOGEE Building Automation Software</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن‌گفتن | یادگیری فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتریان و پرسنلی | مهندسی و فناوری | کامپیوتر و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | طراحی | فیزیک | ریاضیات | مدیریت و سازماندهی | آموزش و پرورش</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | طراحی | فیزیک | ریاضیات | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | درک شفاهی | ثبات دست و بازو | چالاکی انگشتان | تشخیص رنگ بصری | استدلال استقرایی | چالاکی دست | تجسم فضایی | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | انعطاف‌پذیری گسترده | وضوح گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری بستار | درک کتبی | تشخیص گفتار | حساسیت شنوایی | بینایی دور | قدرت تنه | سرعت ادراکی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | درک شفاهی | ثبات دست و بازو | مهارت انگشتان | تشخیص رنگ بصری | استدلال استقرایی | مهارت دستی | تجسم | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت | وضوح گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری بستار | درک کتبی | تشخیص گفتار | حساسیت شنوایی | بینایی دور | قدرت تنه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | ارتباط با دیگران | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | قرارگیری در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | قرارگیری در معرض دماهای بسیار گرم یا سرد | فضای بسته، بدون کنترل محیطی | پیامدهای کاری و نتایج سایر کارگران | صرف زمان به صورت ایستاده | قرارگیری در معرض ارتفاعات بالا | سر و کار داشتن با مشتریان خارجی یا عموم مردم | ایمیل | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | سلامت و ایمنی سایر کارگران | قرارگیری در معرض تجهیزات خطرناک | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرارگیری در معرض شرایط خطرناک | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | نزدیکی فیزیکی</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای ایستادن | قرار گرفتن در معرض ارتفاعات بالا | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکنندگان موتور و سایر ماشین‌آلات | تکنسین‌های زمین‌گرمایی | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عمومی نگهداری و تعمیرات | مهندسان مکانیک | لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | کارگران ورق‌کاری | نصابان و تکنسین‌های خورشیدی حرارتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | مونتاژکاران موتور و سایر ماشین‌آلات | تکنسین‌های زمین‌گرمایی | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عایق‌کاری کف، سقف و دیوار | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران ورق‌کاری | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Intac International Wintac | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | نرم‌افزار پایگاه داده قطعات | RazorSync | نرم‌افزار مسیریابی | ServiceMax | نرم‌افزار مرورگر وب | dESCO ESC</t>
+          <t>Intac International Wintac | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | نرم‌افزار پایگاه داده قطعات | RazorSync | نرم‌افزار نقشه‌برداری مسیر | ServiceMax | نرم‌افزار مرورگر وب | dESCO ESC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش دادن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | مکانیک | زبان انگلیسی | مدیریت و سازماندهی | اداری | کامپیوتر و الکترونیک | فروش و بازاریابی | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | مکانیک | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | فروش و بازاریابی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | حساسیت به مسئله | چالاکی دست | چالاکی انگشتان | بینایی نزدیک | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | تجسم فضایی | انعطاف‌پذیری گسترده | استدلال قیاسی | درک کتبی | استدلال استقرایی | روان بودن ایده‌ها | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | مهارت انگشتان | بینایی نزدیک | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری دامنه حرکت | استدلال قیاسی | درک کتبی | استدلال استقرایی | روانی ایده‌ها | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سر و کار داشتن با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | اهمیت دقیق یا منظم بودن | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | تعیین وظایف، اولویت‌ها و اهداف | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | فضای بسته، کنترل محیطی شده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرارگیری در معرض آلاینده‌ها | قرارگیری در معرض دماهای بسیار گرم یا سرد | فشار زمانی | فضای بسته، بدون کنترل محیطی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان | تمیزکنندگان وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکنندگان تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی وسایل نقلیه موتوری | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورها و متصدیان کوره، کوره پخت، خشک‌کن و دیگ‌های ذوب | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی نگهداری و تعمیرات | مهندسان مکانیک | مکانیک‌های تجهیزات فضای باز و سایر موتورهای کوچک | لوله‌کشان، نصابان لوله و اتصالات و بخارکاران</t>
+          <t>تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان | تمیزکنندگان وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان مکانیک | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | یادگیری فعال | مانیتورینگ | سخن‌گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | طراحی | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>مکانیک | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | طراحی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چالاکی دست | چالاکی انگشتان | دقت کنترل | بینایی نزدیک | زمان عکس‌العمل | ثبات دست و بازو | هماهنگی چند عضو | حساسیت شنوایی | ترتیب‌دهی اطلاعات | توجه انتخابی | تجسم فضایی | توجه شنیداری | انعطاف‌پذیری گسترده | قدرت تنه | قدرت ایستا | استدلال قیاسی | درک کتبی | جهت‌گیری پاسخ | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
+          <t>حساسیت به مسئله | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | زمان عکس‌العمل | ثبات دست و بازو | هماهنگی چند عضو | حساسیت شنوایی | ترتیب‌دهی اطلاعات | توجه انتخابی | تجسم | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | استدلال قیاسی | درک کتبی | جهت‌گیری پاسخ | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرارگیری در معرض آلاینده‌ها | قرارگیری در معرض تجهیزات خطرناک | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان به صورت ایستاده | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فضای بسته، بدون کنترل محیطی | آزادی در تصمیم‌گیری | اهمیت دقیق یا منظم بودن | فشار زمانی | نزدیکی فیزیکی | فضای بسته، کنترل محیطی شده | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و فرم‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود، فرم‌دهی، پرس و متراکم‌سازی | کارگران دستی سایش و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سایش، لپینگ، پرداخت و بافر فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مهندسان نصب ماشین‌آلات (میلو رایت) | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم مدیریت تعمیر و نگهداری کامپیوتری CMMS | نرم‌افزار پایگاه داده | سیستم‌های اطلاعات مدیریت MIS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار برنامه‌ریزی | نرم‌افزار مرورگر وب</t>
+          <t>Computerized maintenance management system software CMMS | نرم‌افزار پایگاه داده | سیستم‌های اطلاعات مدیریت MIS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | مدیریت و سازماندهی | زبان انگلیسی | طراحی</t>
+          <t>مکانیک | تولید و فرآوری | مدیریت و اداره | زبان انگلیسی | طراحی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | حساسیت به مسئله | بینایی نزدیک | چالاکی دست | دقت کنترل | انعطاف‌پذیری گسترده | هماهنگی چند عضو | تجسم فضایی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | چالاکی انگشتان</t>
+          <t>ثبات دست و بازو | حساسیت به مسئله | بینایی نزدیک | مهارت دستی | دقت کنترل | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | تجسم | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرارگیری در معرض آلاینده‌ها | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | صرف زمان به صورت ایستاده | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران | پیامد خطا | قرارگیری در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | ایمیل | قرارگیری در معرض شرایط خطرناک | فضای بسته، بدون کنترل محیطی | فشار زمانی | صرف زمان برای پیاده‌روی یا دویدن | اهمیت تکرار وظایف مشابه | پیامدهای کاری و نتایج سایر کارگران | فضای بسته، کنترل محیطی شده | گفتگوهای تلفنی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | ایمیل | قرار گرفتن در معرض شرایط خطرناک | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی | صرف زمان برای راه رفتن یا دویدن | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج فلز و پلاستیک | کارگران دستی سایش و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سایش، لپینگ، پرداخت و بافر فلز و پلاستیک | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تولید محصولات کاغذی | تعمیرکاران واگن‌های ریلی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد فلز و پلاستیک | تیزکنندگان و فیلرکاران ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تعمیرکنندگان واگن‌های ریلی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | مانیتورینگ | سخن‌گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | ساختمان و ساخت‌وساز | آموزش و پرورش | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | طراحی | تولید و فرآوری | فیزیک | مدیریت و سازماندهی</t>
+          <t>مکانیک | ریاضیات | ساختمان و ساخت‌وساز | آموزش و پرورش | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | طراحی | تولید و فرآوری | فیزیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چالاکی دست | بینایی نزدیک | تجسم فضایی | ثبات دست و بازو | چالاکی انگشتان | دقت کنترل | هماهنگی چند عضو | قدرت ایستا | قدرت تنه | انعطاف‌پذیری گسترده | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | حساسیت شنوایی | بینایی دور | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری پاسخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تعادل کلی بدن | قدرت پویا | کنترل نرخ</t>
+          <t>مهارت دستی | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | قدرت ایستا | قدرت تنه | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | حساسیت شنوایی | بینایی دور | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری پاسخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تعادل کلی بدن | قدرت پویا | کنترل نرخ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فضای بسته، بدون کنترل محیطی | قرارگیری در معرض تجهیزات خطرناک | ارتباط با دیگران | پیامد خطا | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرارگیری در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | گفتگوهای تلفنی | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرارگیری در معرض دماهای بسیار گرم یا سرد | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرارگیری در معرض شرایط نوری بسیار روشن یا نامناسب | ایمیل | پیامدهای کاری و نتایج سایر کارگران | اهمیت تکرار وظایف مشابه | صرف زمان برای خم کردن یا چرخاندن بدن | قرارگیری در معرض ارتفاعات بالا | قرارگیری در معرض شرایط خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، زیر سقف | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | پیامد خطا | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | ایمیل | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض شرایط خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، زیر سقف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | دیگ‌سازان | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | دستیاران--برقی‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی نگهداری و تعمیرات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان اپراتور و سایر اپراتورهای تجهیزات ساخت‌وساز | دکل‌بندها | تکنسین‌های رباتیک | کارگران آهن و فولاد سازه‌ای | سازندگان و مونتاژکنندگان فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | ریگرها | تکنسین‌های رباتیک | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | انعطاف‌پذیری گسترده | هماهنگی چند عضو | دقت کنترل | درک شفاهی | چالاکی دست | قدرت تنه | تعادل کلی بدن | توجه انتخابی | حساسیت به مسئله | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | چالاکی انگشتان | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | درک شفاهی | مهارت دستی | قدرت تنه | تعادل کلی بدن | توجه انتخابی | حساسیت به مسئله | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | مهارت انگشتان | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرارگیری در معرض آلاینده‌ها | فضای بسته، بدون کنترل محیطی | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | قرارگیری در معرض دماهای بسیار گرم یا سرد | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرارگیری در معرض تجهیزات خطرناک | قرارگیری در معرض شرایط نوری بسیار روشن یا نامناسب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرارگیری در معرض شرایط خطرناک | صرف زمان به صورت ایستاده | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | قرارگیری در معرض ارتفاعات بالا | صرف زمان برای پیاده‌روی یا دویدن | درون خودروی روباز یا کار با تجهیزات روباز | آزادی در تصمیم‌گیری | اهمیت دقیق یا منظم بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای ایستادن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای راه رفتن یا دویدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | بناهای آجرکار و بلوک‌کار | بناهای سیمان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | لمینت‌کاران و سازندگان فایبرگلاس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | کارگران دستی سایش و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | دستیاران--بناهای آجرکار، بلوک‌کار، سنگ‌کار و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه فلز | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری فلز و پلاستیک | ذوب‌ریزان و ریخته‌گران فلز | کارگران ورق‌کاری | سازندگان و مونتاژکنندگان فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>دیگ‌سازان | بنّایان آجرکار و بلوک‌کار | بنّایان سیمان‌کار و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | لمینت‌کاران و سازندگان فایبرگلاس | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | ریزندگان و ریخته‌گران فلز | کارگران ورق‌کاری | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bentley MicroStation | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار ایمیل | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Zoom</t>
+          <t>Bentley MicroStation | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار ایمیل | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Zoom</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | مانیتورینگ | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک | خدمات مشتریان و پرسنلی</t>
+          <t>ساختمان و ساخت‌وساز | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل و نقل | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | بینایی نزدیک | استدلال قیاسی | دقت کنترل | درک شفاهی | ترتیب‌دهی اطلاعات | چالاکی دست | چالاکی انگشتان | استدلال استقرایی | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری گسترده | استقامت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | تجسم فضایی | انعطاف‌پذیری بستار | کنترل نرخ | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تشخیص گفتار | درک عمق | تشخیص رنگ بصری | وضوح گفتار</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | بینایی نزدیک | استدلال قیاسی | دقت کنترل | درک شفاهی | ترتیب‌دهی اطلاعات | مهارت دستی | مهارت انگشتان | استدلال استقرایی | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | تجسم | انعطاف‌پذیری بستار | کنترل نرخ | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تشخیص گفتار | درک عمق | تشخیص رنگ بصری | وضوح گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرارگیری در معرض شرایط خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | قرارگیری در معرض ارتفاعات بالا | فراوانی تصمیم‌گیری | قرارگیری در معرض تجهیزات خطرناک | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | اهمیت دقیق یا منظم بودن | ارتباط با دیگران | قرارگیری در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | قرارگیری در معرض شرایط نوری بسیار روشن یا نامناسب | گفتگوهای تلفنی | پیامدهای کاری و نتایج سایر کارگران | درون خودروی روباز یا کار با تجهیزات روباز | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرارگیری در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | صرف زمان به صورت ایستاده | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | فضای بسته، بدون کنترل محیطی | ایمیل | قرارگیری در معرض آلاینده‌ها | سر و کار داشتن با مشتریان خارجی یا عموم مردم | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض ارتفاعات بالا | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | اهمیت دقیق یا درست بودن | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارکنان | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، بدون کنترل شرایط محیطی | ایمیل | قرار گرفتن در معرض آلاینده‌ها | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه‌ها، پست‌های برق و رله‌ها | برقی‌کاران | دستیاران--برقی‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | اپراتورهای بالابر و وینچ | مهندسان اپراتور و سایر اپراتورهای تجهیزات ساخت‌وساز | لوله‌گذاران | لوله‌کشان، نصابان لوله و اتصالات و بخارکاران | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط راه‌آهن | دکل‌بندها | تعمیرکاران سیگنال و سوزن ریل | کارگران آهن و فولاد سازه‌ای | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | اپراتورهای بالابر و وینچ | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | ریگرها | تعمیرکاران سیگنال و سوزن ریل | کارگران سازه‌های آهنی و فولادی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Cisco IOS | نرم‌افزار ایمیل | Mapcom systems M4 | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Ping tools | Slack | نرم‌افزار سیستم پروتکل انتقال صدا از طریق اینترنت VoIP | نرم‌افزار مرورگر وب | نرم‌افزار سیستم مدیریت نیروی کار</t>
+          <t>Autodesk AutoCAD | Cisco IOS | نرم‌افزار ایمیل | Mapcom systems M4 | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Ping tools | Slack | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | نرم‌افزار سیستم مدیریت نیروی کار</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | تفکر انتقادی | مانیتورینگ | گوش دادن فعال</t>
+          <t>سخن گفتن | تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مخابرات | خدمات مشتریان و پرسنلی | زبان انگلیسی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | مکانیک | آموزش و پرورش | ارتباطات و رسانه</t>
+          <t>مخابرات | خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مکانیک | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | انعطاف‌پذیری گسترده | ثبات دست و بازو | حساسیت به مسئله | چالاکی دست | هماهنگی چند عضو | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال قیاسی | توجه انتخابی | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | درک کتبی | وضوح گفتار | بینایی دور | قدرت ایستا | دقت کنترل | چالاکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | هماهنگی چند عضو | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال قیاسی | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | درک کتبی | وضوح گفتار | بینایی دور | قدرت ایستا | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | درون خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | ارتباط با دیگران | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | قرارگیری در معرض آلاینده‌ها | قرارگیری در معرض تجهیزات خطرناک | قرارگیری در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | فضای بسته، بدون کنترل محیطی | قرارگیری در معرض ارتفاعات بالا | سر و کار داشتن با مشتریان خارجی یا عموم مردم | صرف زمان به صورت ایستاده | قرارگیری در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای انجام حرکات تکراری | قرارگیری در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرارگیری در معرض شرایط خطرناک | فضای بسته، کنترل محیطی شده | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، زیر سقف | اهمیت تکرار وظایف مشابه | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض ارتفاعات بالا | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض شرایط خطرناک | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، زیر سقف | اهمیت تکرار وظایف یکسان | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | فناوریست‌ها و تکنسین‌های مهندسی الکتریک و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه‌ها، پست‌های برق و رله‌ها | برقی‌کاران | نصابان و تعمیرکاران تجهیزات الکترونیکی وسایل نقلیه موتوری | دستیاران--برقی‌کاران | اپراتورهای بالابر و وینچ | تکنسین‌های نورپردازی | لوله‌گذاران | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل | نصابان سیستم‌های امنیتی و اعلام حریق | تعمیرکاران سیگنال و سوزن ریل | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
+          <t>نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | برق‌کاران | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | دستیاران--برق‌کاران | اپراتورهای بالابر و وینچ | تکنسین‌های نورپردازی | لوله‌گذاران | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | تعمیرکاران سیگنال و سوزن ریل | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0081_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0081_fa.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت سفارش کار | نرم‌افزار مسیریابی | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | Microsoft Windows | نرم‌افزار مرورگر وب</t>
+          <t>Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب | نرم‌افزار دستور کار</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ساختمان و سازه | مهندسی و فناوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | استحکام تنه | انعطاف‌پذیری بدنی | قدرت ایستا | چابکی انگشتان | درک شفاهی | وضوح گفتار | تشخیص گفتار | هماهنگی چندعضوی | دقت کنترل | مرتب‌سازی اطلاعات | بیان شفاهی | درک کتبی | تجسم فضایی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | ادراک عمق | تشخیص رنگ | تعادل کلی بدن | هماهنگی کلی بدن</t>
+          <t>مهارت دستی | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | قدرت تنه | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | مهارت انگشتان | درک شفاهی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | بیان شفاهی | درک کتبی | تجسم | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک عمق | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیشه خودرو | نجاران | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | برق‌کاران | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | نصابان و تعمیرکاران آسانسور و پله‌برقی | نصابان فنس و نرده | شیشه‌بران و شیشه‌گذاران | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله‌های بخار | عایق‌کاران کف، سقف و دیوار | قفل‌سازان و تعمیرکاران گاوصندوق | کارگران عمومی تعمیرات و نگهداری | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | لوله‌کش‌ها و نصابان لوله‌های آب و بخار | تعمیرکاران واگن‌های قطار | ورق‌کاران و فلزکاران صنعتی | اسکلت‌سازان فلزی و سازه‌های فولادی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصاب و تعمیرکار شیشه خودرو | نجاران و درودگران | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | برق‌کاران | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله‌برقی | نصابان فنس و حصار | شیشه‌بران و نصابان شیشه | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | قفل‌سازان و تعمیرکاران گاوصندوق | کارگران عمومی تعمیرات و نگهداری تاسیسات | مکانیک تجهیزات سنگین متحرک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | تعمیرکار واگن قطار | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | نگارش | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | طراحی | تولید و پردازش</t>
+          <t>مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | طراحی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | بیان شفاهی | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی دستی | تشخیص گفتار | انعطاف‌پذیری بدنی | هماهنگی چندعضوی | چابکی انگشتان | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری بستن ذهنی | دقت کنترل | وضوح گفتار</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | دقت کنترل | وضوح گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان صنعتی | کارشناسان و تکنسین‌های کالیبراسیون | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان مکانیک | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | لوله‌کش‌ها و نصابان لوله‌های آب و بخار | تعمیرکاران واگن‌های قطار | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | دیگ‌سازان و مخزن‌سازان صنعتی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان مکانیک | مکانیک تجهیزات سنگین متحرک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | تعمیرکار واگن قطار | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | طراحی | فیزیک | ریاضیات | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مهندسی و فناوری | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | طراحی | فیزیک | ریاضیات | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | استدلال قیاسی | درک شفاهی | ثبات دست و بازو | چابکی انگشتان | تشخیص رنگ | استدلال استقرایی | چابکی دستی | تجسم فضایی | بیان شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | هماهنگی چندعضوی | انعطاف‌پذیری بدنی | وضوح گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری بستن ذهنی | درک کتبی | تشخیص گفتار | حساسیت شنوایی | دید دور | استحکام تنه | سرعت ادراک</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | درک شفاهی | ثبات دست و بازو | مهارت انگشتان | تشخیص رنگ بصری | استدلال استقرایی | مهارت دستی | تجسم | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | انعطاف‌پذیری دامنه حرکت | وضوح گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری بستار | درک کتبی | تشخیص گفتار | حساسیت شنوایی | بینایی دور | قدرت تنه | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های نیروگاه‌های زیست‌توده | دیگ‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | تکنسین‌های انرژی زمین‌گرمایی | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله‌های بخار | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران کف، سقف و دیوار | کارگران عمومی تعمیرات و نگهداری | مهندسان مکانیک | لوله‌کش‌ها و نصابان لوله‌های آب و بخار | ورق‌کاران و فلزکاران صنعتی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | تکنسین‌های نیروگاه زیست‌توده | دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکاران موتور و سایر ماشین‌آلات | تکنسین‌های سامانه‌های زمین‌گرمایی | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران کف، سقف و دیوار | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان مکانیک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | فروش و بازاریابی | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | مکانیک | زبان انگلیسی | مدیریت و اداره | اداری | رایانه و الکترونیک | فروش و بازاریابی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | چابکی انگشتان | دید نزدیک | بیان شفاهی | درک شفاهی | مرتب‌سازی اطلاعات | تجسم فضایی | انعطاف‌پذیری بدنی | استدلال قیاسی | درک کتبی | استدلال استقرایی | روانی ایده‌ها | بیان کتبی | تشخیص رنگ | استحکام تنه | قدرت ایستا | هماهنگی چندعضوی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستن ذهنی | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | مهارت انگشتان | بینایی نزدیک | بیان شفاهی | درک شفاهی | ترتیب‌دهی اطلاعات | تجسم | انعطاف‌پذیری دامنه حرکت | استدلال قیاسی | درک کتبی | استدلال استقرایی | روانی ایده‌ها | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و مکانیک‌های خدمات خودرو | دیگ‌سازان صنعتی | کارگران نظافت وسایل نقلیه و تجهیزات | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | اپراتورهای کوره، خشک‌کن و دیگ‌های ذوب | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های روشنایی و نورپردازی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری | مهندسان مکانیک | مکانیک‌های ماشین‌آلات و تجهیزات موتوری کوچک | لوله‌کش‌ها و نصابان لوله‌های آب و بخار</t>
+          <t>مکانیک و تکنسین خدمات خودرو | دیگ‌سازان و مخزن‌سازان صنعتی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تکنسین‌های نورپردازی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | مهندسان مکانیک | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | تولید و پردازش | مهندسی و فناوری | طراحی | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | زبان انگلیسی | تولید و فرآوری | مهندسی و فناوری | طراحی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چابکی دستی | چابکی انگشتان | دقت کنترل | دید نزدیک | زمان واکنش | ثبات دست و بازو | هماهنگی چندعضوی | حساسیت شنوایی | مرتب‌سازی اطلاعات | توجه انتخابی | تجسم فضایی | توجه شنوایی | انعطاف‌پذیری بدنی | استحکام تنه | قدرت ایستا | استدلال قیاسی | درک کتبی | جهت‌گیری پاسخ | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
+          <t>حساسیت به مسئله | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | زمان عکس‌العمل | ثبات دست و بازو | هماهنگی چند عضو | حساسیت شنوایی | ترتیب‌دهی اطلاعات | توجه انتخابی | تجسم | توجه شنیداری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | استدلال قیاسی | درک کتبی | جهت‌گیری پاسخ | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک شفاهی | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن، قالب‌گیری، پرس و تراکم مواد | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای پرداخت، سنگ‌زنی و لپینگ فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین فرز و صفحه تراش فلز و پلاستیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب، به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و پردازش | مدیریت و امور اداری | زبان انگلیسی | طراحی</t>
+          <t>مکانیک | تولید و فرآوری | مدیریت و اداره | زبان انگلیسی | طراحی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | حساسیت به مسئله | دید نزدیک | چابکی دستی | دقت کنترل | انعطاف‌پذیری بدنی | هماهنگی چندعضوی | تجسم فضایی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستن ذهنی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص رنگ | استحکام تنه | قدرت ایستا | چابکی انگشتان</t>
+          <t>ثبات دست و بازو | حساسیت به مسئله | بینایی نزدیک | مهارت دستی | دقت کنترل | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | تجسم | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش و اسلایس | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های آهنگری و فورج فلز و پلاستیک | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای پرداخت، سنگ‌زنی و لپینگ فلز و پلاستیک | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان خطوط ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین فرز و صفحه تراش فلز و پلاستیک | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید محصولات کاغذی | تعمیرکاران واگن‌های قطار | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تیزکاران و سنگ‌زن‌های ابزار و سنبه | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب، به‌جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک تجهیزات سنگین متحرک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تعمیرکار واگن قطار | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dassault Systemes SolidWorks | Autodesk AutoCAD | SAP | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+          <t>Dassault Systemes SolidWorks | Autodesk AutoCAD | SAP | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Outlook | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | ساختمان و سازه | آموزش و تدریس | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | طراحی | تولید و پردازش | فیزیک | مدیریت و امور اداری</t>
+          <t>مکانیک | ریاضیات | ساختمان و ساخت‌وساز | آموزش و پرورش | مهندسی و فناوری | ایمنی و امنیت عمومی | زبان انگلیسی | طراحی | تولید و فرآوری | فیزیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | دقت کنترل | هماهنگی چندعضوی | قدرت ایستا | استحکام تنه | انعطاف‌پذیری بدنی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک شفاهی | حساسیت شنوایی | دید دور | زمان واکنش | سرعت ادراک | انعطاف‌پذیری بستن ذهنی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری پاسخ | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | تعادل کلی بدن | قدرت پویا | کنترل نرخ</t>
+          <t>مهارت دستی | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | قدرت ایستا | قدرت تنه | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | حساسیت شنوایی | بینایی دور | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | جهت‌گیری پاسخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | تعادل کلی بدن | قدرت پویا | کنترل نرخ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان صنعتی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | کارگران کمکی برق‌کاران | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری | تنظیم‌کنندگان و اپراتورهای ماشین فرز و صفحه تراش فلز و پلاستیک | مکانیک‌های ماشین‌آلات سنگین متحرک، به‌جز موتور | اپراتورهای ماشین‌آلات و تجهیزات سنگین عمرانی | ریگرها و باربندهای تجهیزات سنگین | تکنسین‌های رباتیک | اسکلت‌سازان فلزی و سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های جوشکاری، لحیم‌کاری و لحیم سخت</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | تکنسین‌های رباتیک | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت نگهداری و تعمیرات | نرم‌افزار ثبت ساعت کارکرد و حضور و غیاب | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
+          <t>نرم‌افزار مدیریت تعمیر و نگهداری | نرم‌افزار ثبت ساعت کارکرد و حضور و غیاب | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | انعطاف‌پذیری بدنی | هماهنگی چندعضوی | دقت کنترل | درک شفاهی | چابکی دستی | استحکام تنه | تعادل کلی بدن | توجه انتخابی | حساسیت به مسئله | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | چابکی انگشتان | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | درک شفاهی | مهارت دستی | قدرت تنه | تعادل کلی بدن | توجه انتخابی | حساسیت به مسئله | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | مهارت انگشتان | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | بناهای آجر و بلوک | بتن‌ریزان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | لایه‌نشان‌ها و سازندگان قطعات فایبرگلاس | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | کارگران سنگ‌زنی و صیقل‌کاری دستی | تنظیم‌کنندگان و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | کارگران کمکی بنایان آجر، بلوک، سنگ و کاشی‌کاران | عایق‌کاران کف، سقف و دیوار | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و مراقبان کوره‌های تصفیه و ذوب فلز | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به‌جز فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های آبکاری فلز و پلاستیک | مذاب‌ریزان و ریخته‌گران فلزات | ورق‌کاران و فلزکاران صنعتی | سازندگان و مونتاژکاران سازه‌های فلزی | کارگران موزاییک‌کاری، پلیمری و پرداخت نهایی کف | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب، به‌جز اره‌کشی</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | بنایان و سفت‌کاران ساختمان | بتن‌ریزان و پرداخت‌کاران بتن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | لایه‌نشانان و سازندگان فایبرگلاس | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | ریخته‌گران و متصدیان بارریزی مذاب فلزات | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک | خدمات مشتریان و خدمات فردی</t>
+          <t>ساختمان و ساخت‌وساز | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل و نقل | مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چندعضوی | دید نزدیک | استدلال قیاسی | دقت کنترل | درک شفاهی | مرتب‌سازی اطلاعات | چابکی دستی | چابکی انگشتان | استدلال استقرایی | دید دور | تعادل کلی بدن | انعطاف‌پذیری بدنی | استقامت بدنی | استحکام تنه | قدرت ایستا | زمان واکنش | جهت‌گیری پاسخ | تجسم فضایی | انعطاف‌پذیری بستن ذهنی | کنترل نرخ | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | تشخیص گفتار | ادراک عمق | تشخیص رنگ | وضوح گفتار</t>
+          <t>حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو | بینایی نزدیک | استدلال قیاسی | دقت کنترل | درک شفاهی | ترتیب‌دهی اطلاعات | مهارت دستی | مهارت انگشتان | استدلال استقرایی | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | جهت‌گیری پاسخ | تجسم | انعطاف‌پذیری بستار | کنترل نرخ | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تشخیص گفتار | درک عمق | تشخیص رنگ بصری | وضوح گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات و تجهیزات کنترلی، به‌جز درب‌های مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | برق‌کاران | کارگران کمکی برق‌کاران | کارگران کمکی نصابان، تعمیرکاران و عوامل نگهداری | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله‌های بخار | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌آلات و تجهیزات سنگین عمرانی | لوله‌گذاران شبکه‌های آب و فاضلاب | لوله‌کش‌ها و نصابان لوله‌های آب و بخار | دیسپاچرها و توزیع‌کنندگان انرژی الکتریکی | اپراتورهای تجهیزات ریلی و نصب خطوط آهن | ریگرها و باربندهای تجهیزات سنگین | تعمیرکاران علائم، سوزن‌ها و سوئیچ‌های راه‌آهن | اسکلت‌سازان فلزی و سازه‌های فولادی | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی | نصابان و کابل‌کشان خطوط مخابراتی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | اپراتورهای بالابر و وینچ | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | لوله‌گذاران خطوط انتقال | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | اسکلت‌سازان و نصابان سازه‌های فولادی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | نظارت | شنیدن فعال</t>
+          <t>سخن گفتن | تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مخابرات | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مکانیک | آموزش و تدریس | ارتباطات و رسانه</t>
+          <t>مخابرات | خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مکانیک | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | انعطاف‌پذیری بدنی | ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | هماهنگی چندعضوی | استحکام تنه | مرتب‌سازی اطلاعات | استدلال قیاسی | توجه انتخابی | تجسم فضایی | سرعت ادراک | انعطاف‌پذیری بستن ذهنی | استدلال استقرایی | درک کتبی | وضوح گفتار | دید دور | قدرت ایستا | دقت کنترل | چابکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | هماهنگی چند عضو | قدرت تنه | ترتیب‌دهی اطلاعات | استدلال قیاسی | توجه انتخابی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | درک کتبی | وضوح گفتار | بینایی دور | قدرت ایستا | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران برق و الکترونیک تجهیزات حمل‌ونقل | تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | برق‌کاران | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | کارگران کمکی برق‌کاران | اپراتورهای بالابر و وینچ | تکنسین‌های روشنایی و نورپردازی | لوله‌گذاران شبکه‌های آب و فاضلاب | دیسپاچرها و توزیع‌کنندگان انرژی الکتریکی | نصابان و تعمیرکاران تجهیزات رادیویی، دکل‌ها و سایت‌های سلولار | نصابان سیستم‌های دزدگیر، امنیتی و اعلام حریق | تعمیرکاران علائم، سوزن‌ها و سوئیچ‌های راه‌آهن | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | برق‌کاران | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | کمک‌برق‌کاران | اپراتورهای بالابر و وینچ | تکنسین‌های نورپردازی | لوله‌گذاران خطوط انتقال | دیسپچرها و توزیع‌کنندگان شبکه برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصاب سیستم‌های اعلام سرقت و حریق | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
